--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_013/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_013/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,6 +364,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -434,6 +454,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -505,6 +530,11 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1306,12 +1336,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS CFD for preliminary performance prediction of NASA Rotor 37 at 98–102% design speed near peak efficiency</t>
+          <t>Steady RANS CFD performance prediction of NASA Rotor 37 at near-design speed for PDR-level margin allocation</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Ansys CFX 2023 R2 steady RANS (k-ω SST) single-passage simulations of NASA Rotor 37 used to predict total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles at near-design rotational speeds for PDR-level margin allocation and compressor map placement. Stall boundary mapping and detailed loss decomposition are explicitly excluded from scope.</t>
+          <t>Ansys CFX 2023 R2 steady RANS simulations of the NASA Rotor 37 single-stage transonic axial compressor are used to predict mass-averaged total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles at 98–102% design rotational speed. Results inform preliminary design review (PDR) margin allocations and operating map placement. Stall boundary mapping and detailed loss decomposition are explicitly out of scope.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1349,9 +1379,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>CAR-ROTOR37-CFD-001 Rev B (2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1412,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>PDR Performance Prediction Acceptability Thresholds</t>
+          <t>PDR Performance Acceptability Thresholds</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1480,7 +1510,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Agreed acceptability criteria for PDR use: total pressure ratio within ±2.0% of test at 98–102% design speed near peak efficiency; adiabatic efficiency within ±2.5 percentage points; spanwise exit flow angle within ±1.5° at 50% and 90% span; choke mass flow within ±1.5%.</t>
+          <t>Agreed acceptability margins for PDR use: total pressure ratio within ±2.0% of test at 98–102% design speed near peak efficiency; adiabatic efficiency within ±2.5 percentage points; spanwise exit flow angle within ±1.5° at 50% and 90% span; choke mass flow within ±1.5%. Use beyond these conditions (stall proximity, speeds below 95%) is explicitly excluded.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1502,12 +1532,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys CFX 2023 R2 Steady RANS SST Model</t>
+          <t>Ansys CFX 2023 R2 Steady RANS SST Model — NASA Rotor 37</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Double-precision steady RANS with k-ω SST and curvature correction; multi-block hexahedral single-passage domain; 3.4M-cell medium grid; mixing-plane interface; adiabatic no-slip walls; second-order spatial discretization.</t>
+          <t>Multi-block hexahedral single-passage RANS model (3.4M cells, k–ω SST with curvature correction, second-order spatial discretization, mixing-plane downstream boundary, adiabatic walls, y+ ≈ 1) used to predict compressor performance at near-design speed.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1554,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Public NASA Rotor 37 rig measurements including total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles at 98% and 100% design speed; geometry blade coordinates, hub/shroud contours, and tip-clearance bench measurements.</t>
+          <t>Published NASA Rotor 37 blade geometry, hub/shroud contours, and rig measurements at 100% and 98% design speed including spanwise pressure, flow angle, and Mach profiles; pressure ratio, efficiency, and choke mass flow from calibrated instrumentation (Rosemount transducers, Type-T thermocouples).</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1566,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>UQ Surrogate and Sensitivity Analysis Dataset</t>
+          <t>Latin Hypercube Sampling UQ Dataset</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>250-sample Latin Hypercube Sampling dataset used to build Gaussian process surrogate (R² = 0.985 for PR, 0.972 for efficiency); Sobol sensitivity indices and 95% propagated uncertainty bands for tip clearance, inlet T0/P0, turbulence intensity, and blade clocking.</t>
+          <t>250-sample LHS uncertainty propagation dataset covering tip clearance, inlet total pressure and temperature (correlated), turbulence intensity, and blade clocking offset; surrogate (Gaussian process, 5-fold CV R² = 0.985 PR, 0.972 η) used to compute 95% output uncertainty bands and Sobol-like sensitivity indices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Three-Level Grid Convergence Study Dataset</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Coarse (1.2M), medium (3.4M), and fine (9.1M) cell mesh solutions at 100% design speed near peak efficiency; GCI computed for pressure ratio (0.85%), adiabatic efficiency (1.2%), and exit flow angle at 90% span (1.6%).</t>
         </is>
       </c>
     </row>
@@ -1978,7 +2025,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Three-Level Grid Convergence Study (GCI)</t>
+          <t>Operating Map Pressure Ratio and Choke Flow Comparison</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1993,12 +2040,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Mesh convergence study at 100% design speed near peak efficiency using coarse (1.2M), medium (3.4M), and fine (9.1M) cell grids. Richardson extrapolation and Grid Convergence Index computed for total pressure ratio, adiabatic efficiency, and exit flow angle at 90% span.</t>
+          <t>Steady RANS predictions of total pressure ratio at peak efficiency and choke mass flow at 100% design speed compared against NASA Rotor 37 rig measurements</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated values; apparent order of convergence ~1.88–1.95</t>
+          <t>NASA Rotor 37 experimental rig data (pressure ratio, choke mass flow)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2008,12 +2055,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI), Richardson extrapolation</t>
+          <t>Test uncertainty bands (±0.8% pressure ratio reported); CFD 95% propagated uncertainty via LHS surrogate (PR ±0.031)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>GCI (95% conf.): PR = 0.85%, efficiency = 1.2%, exit flow angle = 1.6%; apparent order p ≈ 1.74–1.95</t>
+          <t>PR error +1.5% (within ±2.0% target); choke mass flow error +1.3% (within ±1.5% target)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2025,7 +2072,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Check</t>
+          <t>Spanwise Exit Profile Comparison</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2035,22 +2082,27 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>RMS residuals monitored to &lt; 1e-5; mass imbalance &lt; 0.02%; mixing-plane flux mismatch &lt; 0.05%; integral quantities steady to &lt; 0.05% over 2000 iterations; restart continuation confirmed iterative error &lt; 0.1% on integral metrics.</t>
+          <t>Comparison of predicted spanwise distributions of total pressure, exit flow angle, and Mach number at rotor exit plane (x/Cax = 1.5) against rig rake data at 100% design speed</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Internal convergence criteria defined in V&amp;V plan</t>
+          <t>NASA Rotor 37 spanwise rake measurements at rotor exit</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Test measurement uncertainty bands overlaid; numerical discretization uncertainty from GCI applied</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Mass imbalance &lt; 0.02%; iterative error &lt; 0.1% on integral metrics; residuals &gt; 4 orders reduction</t>
+          <t>Total pressure within ±1.5% (10–90% span); flow angle within ±1.2° at 50% and 90% span (target ±1.5°); Mach shock strength ±0.03; overprediction near 90–95% span; hub corner deviation 1.8° at 20% span</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2062,7 +2114,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Validation Against NASA Rotor 37 Rig Data (Design Window)</t>
+          <t>Adiabatic Efficiency Comparison</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2072,12 +2124,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>CFD predictions (medium grid) compared to NASA rig measurements at 98% and 100% design speed: total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles of total pressure, flow angle, and Mach number. Two anomalous low-flow data points at 98% speed excluded as non-representative.</t>
+          <t>Predicted adiabatic efficiency at near-peak-efficiency condition (100% design speed) compared to NASA rig measurement</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>NASA Rotor 37 experimental rig data (calibrated instrumentation, ±0.8% PR uncertainty)</t>
+          <t>NASA Rotor 37 rig efficiency measurement</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2087,12 +2139,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Experimental uncertainty bands from calibrated instrumentation; 95% combined output uncertainty from LHS/GP surrogate propagation</t>
+          <t>LHS surrogate propagation (95% CI η ±0.021); GCI contribution ±1.2 percentage points</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>PR error +1.5% (target ±2.0%); efficiency error +2.1 p.p. (target ±2.5 p.p.); choke mass flow +1.3% (target ±1.5%); exit flow angle within ±1.2° at 50% and 90% span (target ±1.5°); 95% PR uncertainty ±0.031; 95% efficiency uncertainty ±0.021</t>
+          <t>CFD η = 0.822 vs test; bias +2.1 percentage points (within ±2.5 p.p. target)</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2104,7 +2156,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Cross-Code Comparison — SU2 vs CFX at Design Point</t>
+          <t>Three-Level Grid Convergence Study (GCI)</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2114,22 +2166,27 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>One design-flow-rate point replicated independently in SU2 v8.0.1 (RANS SST, 3.2M-cell grid, matched wall spacing) by an engineer external to the project team. Compared pressure ratio, efficiency, exit flow angle at 90% span, and shock location.</t>
+          <t>Richardson extrapolation and GCI computed for pressure ratio, adiabatic efficiency, and exit flow angle using coarse, medium, and fine grids at 100% design speed</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Ansys CFX 2023 R2 medium-grid result at the same design point</t>
+          <t>Richardson extrapolated values; apparent order of convergence</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (95% confidence), Richardson extrapolation; apparent order p = 1.88–1.95</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>PR difference 0.7%; efficiency difference 0.5 p.p.; exit flow angle difference 0.6° at 90% span; shock location discrepancy &lt; 1.5% chord</t>
+          <t>GCI (fine-grid relative): PR 0.85%, η 1.2%, exit flow angle 90% span 1.6%; iterative error &lt;0.1% on integral metrics</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2141,7 +2198,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Numerical Code Verification — MMS and Isentropic Nozzle Benchmarks</t>
+          <t>Cross-Code Verification — SU2 Comparison</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2151,12 +2208,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>2D subsonic/vortex Method of Manufactured Solutions (MMS) case and inviscid isentropic nozzle benchmark executed in CFX 2023 R2. Observed L2 error reduction rates measured across a series of structured meshes.</t>
+          <t>One design-flow-point replicated in SU2 v8.0.1 (RANS SST) on a 3.2M-cell grid with matched wall spacing by an independent engineer; results compared to CFX medium-grid solution</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Analytical solutions; expected second-order convergence rate</t>
+          <t>Ansys CFX 2023 R2 medium-grid solution</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2166,7 +2223,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Observed order ~1.97 for linear elements; ~2.85 with curvature-based reconstruction</t>
+          <t>PR difference 0.7%; efficiency difference 0.5 p.p.; exit flow angle difference 0.6° at 90% span; shock location discrepancy &lt;1.5% chord</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2320,12 +2377,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented regression testing; version control; reproducibility demonstrated</t>
+          <t>Commercial solver has passed vendor regression suite; in-house benchmarks confirm expected numerical order; version control and CI pipeline in place</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys CFX 2023 R2 passed the vendor's regression suite for compressible flows. All meshes, case files, and scripts are tracked in GitLab (repo cfd-rotor37, tag v1.3.2). A CI pipeline validates a YAML manifest before runs are dispatched. An independent rerun on different nodes reproduced pressure ratio within 0.03% and efficiency within 0.05 p.p. Analyst completed Ansys-certified training (2025) and internal best-practice refresher (2026). Roles and responsibilities documented in V&amp;V plan (VV-PLN-ROTOR37-2026-01).</t>
+          <t>Ansys CFX 2023 R2 passed vendor regression suite for compressible flows. In-house 2D subsonic/vortex MMS and inviscid isentropic nozzle benchmarks confirm spatial order ~1.97 (linear) and ~2.85 (curvature-based reconstruction). All meshes, case files, and scripts tracked in GitLab (repo 3841, tag v1.3.2); a YAML manifest and CI pipeline validate solver version, turbulence options, and convergence criteria before dispatch. Reproducibility check on different nodes gave PR within 0.03% and η within 0.05 p.p. Analyst completed Ansys-certified CFX training (2025) and internal best-practice refresher (2026). Roles and responsibilities documented in V&amp;V plan VV-PLN-ROTOR37-2026-01.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2354,12 +2411,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Demonstration of correct solution of governing equations via benchmark or MMS; observed order consistent with nominal scheme order</t>
+          <t>Observed spatial order of accuracy consistent with nominal order of scheme; benchmark or MMS results documented</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>2D subsonic/vortex MMS and inviscid isentropic nozzle benchmarks executed in CFX 2023 R2; observed L2 convergence order ~1.97 (linear elements) and ~2.85 (curvature-based reconstruction), consistent with second-order design. Cross-code comparison with SU2 v8.0.1 at the design point showed PR difference 0.7% and efficiency 0.5 p.p., providing additional code-to-code confirmation. No deviations from standard solver were made.</t>
+          <t>In-house MMS (2D subsonic/vortex) and isentropic nozzle benchmarks on a series of structured meshes show L2 error reducing at ~1.97 order (linear elements) and ~2.85 (curvature-based reconstruction), consistent with the second-order spatial scheme. Cross-code comparison with SU2 v8.0.1 (RANS SST, 3.2M-cell grid) at one design flow point yielded PR difference 0.7%, η difference 0.5 p.p., and exit flow angle difference 0.6° at 90% span, with shock location discrepancy &lt;1.5% chord. Independent replication documented in review note Doc R37-IND-CHK-2026-07.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2388,12 +2445,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with GCI reported; discretization uncertainty quantified relative to acceptance thresholds</t>
+          <t>GCI &lt; 1% for primary QoIs; apparent order consistent with nominal scheme order; tip-gap resolution documented</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level (1.2M, 3.4M, 9.1M cell) grid refinement study performed at 100% design speed. GCI (95% confidence) reported: PR = 0.85%, efficiency = 1.2%, exit flow angle = 1.6%. Apparent order p = 1.74–1.95 across QoIs. Richardson extrapolation provides best estimates. Tip-leakage vortex core varied &lt; 0.3% span between medium and fine grids. Discretization uncertainty is subdominant to tip-clearance input uncertainty for primary metrics.</t>
+          <t>Three-level grid study (1.2M, 3.4M, 9.1M cells) at 100% design speed. Apparent order p = 1.88–1.95 for PR and η. GCI (95%) relative to fine grid: PR 0.85%, η 1.2%, exit flow angle at 90% span 1.6%. Richardson-extrapolated PR = 2.110. Tip-leakage vortex core location varied &lt;0.3% span between medium and fine grids. Tip gap resolved with 28 cells (medium) and 52 cells (fine) radially. y+ ≈ 1 across 98% wetted area. Iterative error confirmed &lt;0.1% on integral metrics via restart continuation. Memo MESH-ROT37-2026-02 and repo /mesh_study/design100p/ archive all details.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2422,12 +2479,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals and mass balance meet specified convergence criteria; iterative error confirmed small relative to discretization and validation errors</t>
+          <t>RMS residuals below 1e-5; mass imbalance &lt;0.1%; integral quantities stationary over final iterations</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>RMS residuals &lt; 1e-5 (continuity and momentum &gt; 4 orders reduction; turbulence &gt; 3.5 orders). Mass imbalance &lt; 0.02%. Mixing-plane flux mismatch &lt; 0.05%. Integral quantities steady to &lt; 0.05% over 2000 iterations. Restart continuation on each grid confirmed iterative error &lt; 0.1% on integral metrics, which is well below GCI and validation error magnitudes.</t>
+          <t>RMS residuals converged &gt;4 orders (continuity, momentum) and &gt;3.5 orders (turbulence equations). Mass imbalance across inlet/outlet &lt;0.02%. Mixing-plane flux mismatch &lt;0.05%. Integral QoIs steady to &lt;0.05% over 2000 iterations. Restart continuation on each grid level confirmed iterative error &lt;0.1% on pressure ratio and efficiency. Convergence judged on forces and integral metrics, not residuals alone (Appendix A checklist).</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2456,12 +2513,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review performed; boundary conditions and model setup verified; pre-run checklist completed without deviations</t>
+          <t>Independent review of model setup; boundary conditions verified; pre-run checklist completed with no deviations; post-processing planes matched to rig locations</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>A pre-run QA checklist covering 11 unit conversions and 7 vector directions flagged zero inconsistencies. Appendix A documents explicit sign-off on rotation direction, frame change, hub/shroud BCs, inlet reference frame, blade count/pitch, post-processing plane alignment, and convergence criteria. Cold-eyes review by Aerodynamics Methods Working Group (2026-07-02) raised two actions (turbulent assumption justification; inlet turbulence sensitivity), both closed 2026-07-15. Independent SU2 replication by a separate engineer provided external check (Doc R37-IND-CHK-2026-07).</t>
+          <t>Pre-run QA checklist verified rotation sign/magnitude, frame change at mixing plane, hub/shroud no-slip adiabatic BC, inlet swirl convention, blade count/pitch, turbulence intensity and length scale, unit consistency (11 conversions, 7 vector directions — zero flagged), and post-processing planes matched to rig rake locations. Cold-eyes review by Aerodynamics Methods Working Group (2026-07-02); two actions raised (turbulent assumption justification, inlet turbulence sensitivity), both closed 2026-07-15. Independent replication by separate engineer in SU2 (Doc R37-IND-CHK-2026-07). No deviations recorded in any checklist item.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2490,12 +2547,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified for the flow regime; known limitations documented; sensitivity to modeling choices quantified</t>
+          <t>Governing equations and turbulence closure justified for the flow regime; known limitations documented; sensitivity to modeling choices quantified</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady RANS with k-ω SST and curvature correction selected and justified: better captures adverse pressure-gradient separation and shock-induced BL thickening than SA in prior studies; curvature correction suppresses spurious production in swirling regions. SA-BCM swap increased efficiency +0.9 p.p. and moved shock 1.1% chord; SST retained due to better spanwise loss agreement. Transitional (γ–Reθ) trial shifted losses &lt; 0.3 p.p.; fully turbulent assumption retained. Adiabatic wall assumption justified (wall heat flux &lt; 0.5% total enthalpy flux). Roughness sensitivity &lt; 0.1 p.p. Model-form limitations (stall, unsteady tip-leakage–shock interaction near 90% span) explicitly documented. Boundary scheme and limiter sensitivity also quantified. Residual shock–tip-leakage bias near 90% span noted as open risk item.</t>
+          <t>k–ω SST with curvature correction selected based on prior compressor studies showing better adverse-pressure-gradient and shock-induced BL thickening performance than SA; curvature correction suppresses spurious production in swirling regions. SA-BCM swap explored: efficiency +0.9 p.p., shock +1.1% chord, PR +0.6% — SST retained for better spanwise loss agreement. Steady RANS justified for time-averaged design-point outputs; fully turbulent assumption validated by transitional (γ–Reθ) sensitivity (&lt;0.3 p.p. loss shift, &lt;1% chord shock movement). Adiabatic wall, ideal gas, and no-roughness assumptions quantitatively justified. Off-design limitations (stall, below 95% speed) explicitly documented. Residual model-form uncertainty in shock–tip-leakage interaction near 90% span identified as open risk item with planned unsteady RANS follow-on.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2524,12 +2581,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Geometry, boundary conditions, and material properties well-characterized with documented uncertainty; key input correlations identified and modeled</t>
+          <t>Geometry sourced from authoritative data; operating conditions from calibrated instrumentation with stated uncertainties; secondary parameters explored via sensitivity analysis</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Blade geometry from NASA TM-xxxx; spline smoothing within ±8 µm of nominal confirmed by surface deviation audit; independent transcription of tip clearance agreed within 1 µm RMS. Inlet P0 and T0 from calibrated Rosemount transducers and Type-T thermocouples (±0.5% FS, ±0.3 K). P0–T0 correlation (ρ = 0.38) and speed–T0 correlation (ρ = 0.21) explicitly modeled. Inlet turbulence intensity (3–7%) range explored; triangular distribution applied in UQ. Blade clocking and tip clearance uncertainty ranges defined. Gas model (ideal gas, γ = 1.4, Sutherland viscosity) justified. Moving-average filter applied to correct plenum drift. Synchronized P0–T0 pairs used for validation boundary conditions.</t>
+          <t>Blade coordinates and hub/shroud contours from NASA TM public data set; spline smoothing within ±8 µm confirmed by surface deviation audit; independent transcription agreed within 1 µm RMS for tip clearance. P0,in and T0,in from calibrated Rosemount transducers (±0.5% FS) and Type-T thermocouples (±0.3 K). Correlation ρ = 0.38 between P0 and T0 derived from concurrent time histories and applied in UQ. Inlet turbulence intensity not directly measured; 3–7% range explored; sensitivity contribution quantified (Sobol index 0.14 PR, 0.19 η). Speed–T0 thermal soak correlation ρ = 0.21 included. Blade chordwise offset ±0.02° (manufacturing clocking) included in LHS. Outlier data points flagged in test documentation and excluded from comparisons. Moving-average filter applied to align CFD steady-state comparisons with quasi-steadied rig values.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2558,12 +2615,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles adequately characterized; sample configuration representative of the modeled geometry</t>
+          <t>Test article is documented production-representative hardware with known geometry; key dimensional parameters (tip clearance) measured and recorded</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>NASA Rotor 37 rig is a well-established public benchmark with documented blade geometry, hub/shroud contours, and bench-measured tip clearance (R37 Bench Cal 1983-04). Blade surface roughness documented (&lt; 0.5 µm Ra). Configuration is rotor-alone with no stator, consistent with the single-passage model. Two anomalous data points at 98% speed (anomalous torque) were identified and excluded with justification. The test dataset originates from a single historical rig campaign; no new physical specimens were procured for this study.</t>
+          <t>The NASA Rotor 37 rig is a well-documented, widely used compressor benchmark; blade geometry is the nominal NASA design. Tip clearance measured from original NASA bench calibration log ("R37 Bench Cal 1983-04") confirmed by independent transcription to 1 µm RMS. Polished blades with Ra &lt; 0.5 µm confirmed; no trip dots. The dataset spans 100% and 98% design speed with documented outlier exclusion. No statistical characterization of a sample population is applicable (single rig), but the hardware pedigree and documentation are strong for this class of benchmark validation.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2585,19 +2642,19 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions measured with calibrated instruments; measurement uncertainties reported; data quality control applied</t>
+          <t>Calibrated instrumentation with stated measurement uncertainties; environmental conditions documented; data quality controls applied</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated Rosemount pressure transducers (±0.5% FS) and Type-T thermocouples (±0.3 K) used in the NASA test. Instrumentation accuracy reported. Barometer drift corrected using logged plenum measurements. Moving-average filter (1 s window) applied to align CFD steady-state with quasi-steadied rig values. Experimental uncertainty bands (e.g., ±0.8% for pressure ratio) are documented and shown in the analysis record. Boundary-layer trip state and blade surface condition documented. Data digitized from NASA reports and cross-checked against tabular appendices.</t>
+          <t>Inlet total pressure measured with calibrated Rosemount transducers (±0.5% FS); inlet total temperature with Type-T thermocouples (±0.3 K). Test uncertainty for pressure ratio reported as ±0.8%. Plenum barometer drift corrected using logged measurements. Low-frequency drift in P0 and T0 addressed by moving-average filter (window 1 s). Synchronized P0–T0 pairs used to set CFD inlet state in validation comparisons. Two anomalous torque data points at 98% speed excluded with documented rationale. Calibration lineage and data quality controls are well-documented in the report.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2626,12 +2683,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD boundary conditions demonstrably matched to experimental inlet and operating conditions; input uncertainty propagation accounts for measurement uncertainties</t>
+          <t>CFD boundary conditions set to match measured rig conditions; input uncertainty propagated consistently between test and simulation; correlation structure preserved</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Inlet P0 and T0 for CFD set from synchronized test timeline pairs, including plenum drift correction. Tip clearance set to bench-measured value (0.356 mm). Outlet static pressure adjusted to match target flow points on the operating map. Fillets omitted per test configuration. No pre-swirl applied, matching test configuration. P0–T0 and speed–T0 correlations from test records included in UQ propagation. Post-processing planes matched to rig rake locations (confirmed in pre-run checklist). Input uncertainty ranges derived from reported instrumentation accuracies.</t>
+          <t>CFD inlet P0 and T0 set directly from synchronized rig measurements; correlation ρ = 0.38 between P0 and T0 included in UQ propagation. Tip clearance set to 0.356 mm from bench measurement (0.356 ± 0.02 mm uncertainty range in LHS). Turbulence intensity matched to estimated rig range (3–7%) with 5% nominal. Post-processing planes confirmed matched to rig rake locations (Appendix A). Speed–T0 correlation ρ = 0.21 applied. Inlet reference frame (no pre-swirl) confirmed. Surrogate-based UQ explicitly maps input uncertainty to output uncertainty for all primary QoIs.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2660,12 +2717,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of CFD predictions to experimental data for all primary QoIs; combined uncertainties assessed; predictions within agreed acceptance thresholds</t>
+          <t>Quantitative error metrics reported for all primary QoIs; 95% uncertainty bands overlap test intervals; multiple operating points compared; spanwise profile comparisons included</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparisons at 98% and 100% design speed: PR +1.5% (target ±2.0%); efficiency +2.1 p.p. (target ±2.5 p.p.); choke mass flow +1.3% (target ±1.5%); exit flow angle within ±1.2° at 50% and 90% span (target ±1.5°). Spanwise total pressure within ±1.5% over 10–90% span. Mach number shock-strength matched to ±0.03. Combined 95% output uncertainty bands (numerical + input + surrogate) overlap experimental intervals for all primary metrics. Larger deviations at 20% span (1.8°, hub corner separation) and 90–95% span (tip-leakage overprediction) documented. Off-design exceedances (efficiency deviation 3.3 p.p. at 95% speed near stall) correctly identified as outside scope.</t>
+          <t>Pressure ratio at peak efficiency: CFD 2.099 vs test 2.068 (+1.5%, within ±2.0% target). Adiabatic efficiency: bias +2.1 p.p. (within ±2.5 p.p. target). Choke mass flow: +1.3% (within ±1.5% target). Spanwise total pressure within ±1.5% over 10–90% span; flow angle within ±1.2° at 50% and 90% span; Mach shock strength ±0.03. Combined 95% uncertainty bands (PR ±0.031, η ±0.021) overlap test intervals for all primary metrics. Comparisons made at 100% and 98% design speed with multiple flow points. Off-design degradation (95% speed, η deviation 3.3 p.p.) documented and correctly excluded from the accepted COU envelope. Test uncertainty bands shown explicitly in analysis record.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2694,12 +2751,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model QoIs directly address PDR performance and margin allocation needs; QoIs are measurable both computationally and experimentally</t>
+          <t>QoIs directly address the PDR performance decision; all QoIs are measurable both computationally and experimentally; acceptability thresholds agreed with systems team</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Primary QoIs — mass-averaged total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles of flow angle, Mach number, and total pressure — directly address the PDR margin allocation and map placement purpose. All QoIs are computed in CFD using mass-averaging or area-averaging on planes matched to rig rake locations, and were directly measured in the NASA Rotor 37 rig campaign. Acceptability thresholds for each QoI were agreed with the systems team (2026-06-11) prior to execution. No surrogate QoIs or indirect metrics are used.</t>
+          <t>The four primary QoIs — mass-averaged total pressure ratio, adiabatic efficiency, choke mass flow, and spanwise exit profiles (flow angle, Mach, total pressure) — are precisely those needed for PDR margin allocation and map placement. Acceptability thresholds were formally agreed with the systems team on 2026-06-11 and are quantitative. All QoIs are directly computed from the CFD solution and directly measured in the NASA rig. The report notes that QoIs outside the PDR scope (stall boundary, detailed loss decomposition, heat transfer) are not claimed.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2728,12 +2785,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (speed, flow regime, geometry, physics) match the intended COU operating window; gaps documented with risk assessment</t>
+          <t>Validation geometry, turbulence regime, speed range, and flow coefficient range match the intended COU; gaps to COU envelope documented</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation performed using the exact geometry and configuration (NASA Rotor 37 rotor-alone, polished blades, measured tip clearance) at 98% and 100% design speed near peak efficiency — directly within the stated COU window of 98–102% design speed. Physics regime (transonic, shock-dominated, tip-leakage) matches. Coverage at 102% speed is limited to three flow points (noted as open issue). Off-design regime (&lt; 95% speed, stall proximity) is explicitly outside the COU and confirmed to exceed error budget; appropriate boundary of applicability is documented. Cross-code comparison with SU2 at the design point provides additional confirmation. Planned extension to 102% speed and unsteady RANS for CDR noted as future actions.</t>
+          <t>Validation uses the same NASA Rotor 37 geometry, same solver setup, same operating speed range (98–102% design speed), and same flow regime as the COU. Spanwise profiles compared at the same axial rake location as the rig. Test data at 100% and 98% speed directly cover the COU window. Known gaps: validation breadth at 102% speed is limited to three flow points (open risk item); shock–tip-leakage interaction near 90% span has residual model-form uncertainty; off-design regime (below 95% speed) is explicitly excluded from the COU with documented evidence of RANS breakdown. Planned actions (unsteady RANS test, CDR expansion) noted for future credibility improvement.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2918,7 +2975,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>All primary QoIs (total pressure ratio +1.5%, adiabatic efficiency +2.1 p.p., choke mass flow +1.3%, exit flow angle within ±1.2° at specified spans) fall within the agreed PDR acceptability thresholds for 98–102% design speed near peak efficiency. Combined 95% uncertainty bands overlap experimental intervals for all metrics. Numerical discretization error is subdominant; iterative convergence is well-controlled; independent replication and peer review are complete. Residual risks (shock–tip-leakage model-form bias near 90% span; limited 102% speed validation coverage) are documented as open items accepted by the Chief Engineer (memo CHENG-PROP-2026-15). Use is restricted to the stated operating window; stall proximity and off-design speeds below 95% are excluded and require additional unsteady simulation.</t>
+          <t>All primary QoIs (total pressure ratio +1.5%, adiabatic efficiency +2.1 p.p., choke mass flow +1.3%, spanwise exit flow angle within ±1.2° at specified spans) fall within the agreed PDR acceptability thresholds at 98–102% design speed near peak efficiency. Quantified 95% combined uncertainty bands overlap test intervals for all metrics. Numerical errors are subdominant (GCI PR 0.85%, η 1.2%). Independent cross-code replication (SU2) and peer review confirm setup correctness. Version-controlled, reproducible, and auditable workflow with CI pipeline in place. Residual risks (shock–tip-leakage interaction near 90% span, limited 102% speed coverage) are documented as open items with planned follow-on actions and accepted by Chief Engineer memo CHENG-PROP-2026-15. Use is accepted for PDR-level performance estimates within the stated domain (98–102% design speed, near-peak efficiency flows); extension to stall proximity or speeds below 95% requires additional unsteady simulation.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
